--- a/early_data/out/footbag_results_pre1997_v1.xlsx
+++ b/early_data/out/footbag_results_pre1997_v1.xlsx
@@ -103,12 +103,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -166,10 +166,10 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -751,7 +751,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Dataset version: v1.0  |  Generated: 2026-03-23</t>
+          <t>Dataset version: v1.0  |  Generated: 2026-03-30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Sources: FBW|OLD_RESULTS  |  ID: 88ab188635  |  CONFIRMED_MULTI_SOURCE</t>
+          <t>Sources: FBW|OLD_RESULTS  |  ID: 1985_worlds  |  CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
     </row>
@@ -1582,35 +1582,35 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="n">
+      <c r="A30" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>Randy Ross / James Stallcup</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>Randy Ross / James Stallcup</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>NEW_PLAYER / NEW_PLAYER</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr">
         <is>
           <t>OLD_RESULTS</t>
         </is>
       </c>
-      <c r="F30" s="17" t="inlineStr">
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>1295f2ff68</t>
         </is>
       </c>
-      <c r="G30" s="17" t="inlineStr">
+      <c r="G30" s="16" t="inlineStr">
         <is>
           <t>046fa84f-2797-5d25-866e-4d04c12880dd / d84a8f26-14f2-5966-b09c-971a685c6c50</t>
         </is>
@@ -2038,35 +2038,35 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="17" t="n">
+      <c r="A46" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B46" s="17" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>Doug Little</t>
         </is>
       </c>
-      <c r="C46" s="17" t="inlineStr">
+      <c r="C46" s="16" t="inlineStr">
         <is>
           <t>Doug Little</t>
         </is>
       </c>
-      <c r="D46" s="17" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>NEW_PLAYER</t>
         </is>
       </c>
-      <c r="E46" s="17" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F46" s="17" t="inlineStr">
+      <c r="E46" s="16" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="F46" s="16" t="inlineStr">
         <is>
           <t>4dacb9d585</t>
         </is>
       </c>
-      <c r="G46" s="17" t="inlineStr">
+      <c r="G46" s="16" t="inlineStr">
         <is>
           <t>d86e1aad-2058-5773-95eb-c5fd05217112</t>
         </is>
@@ -4098,7 +4098,7 @@
     <row r="117">
       <c r="A117" s="12" t="inlineStr">
         <is>
-          <t>Sources: FBW|OLD_RESULTS  |  ID: 1c74083104  |  CONFIRMED_MULTI_SOURCE</t>
+          <t>Sources: FBW|OLD_RESULTS  |  ID: 1985_wfa_nationals  |  CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Location: Golden, Colorado  |  Sources: FBW|OLD_RESULTS  |  ID: b4b6a194e2  |  CONFIRMED_MULTI_SOURCE</t>
+          <t>Location: Golden, Colorado  |  Sources: FBW|OLD_RESULTS  |  ID: 1986_worlds_golden  |  CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
     </row>
@@ -6745,35 +6745,35 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="n">
+      <c r="A23" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>Doug Little</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>Doug Little</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>NEW_PLAYER</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>a31d11ed12</t>
         </is>
       </c>
-      <c r="G23" s="17" t="inlineStr">
+      <c r="G23" s="16" t="inlineStr">
         <is>
           <t>d86e1aad-2058-5773-95eb-c5fd05217112</t>
         </is>
@@ -7271,35 +7271,35 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="17" t="n">
+      <c r="A41" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B41" s="17" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>Ken Eldrick</t>
         </is>
       </c>
-      <c r="C41" s="17" t="inlineStr">
+      <c r="C41" s="16" t="inlineStr">
         <is>
           <t>Ken Eldrick</t>
         </is>
       </c>
-      <c r="D41" s="17" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>NEW_PLAYER</t>
         </is>
       </c>
-      <c r="E41" s="17" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F41" s="17" t="inlineStr">
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
         <is>
           <t>a31d11ed12</t>
         </is>
       </c>
-      <c r="G41" s="17" t="inlineStr">
+      <c r="G41" s="16" t="inlineStr">
         <is>
           <t>03bcdedb-b187-5ef3-ba2d-e371c1cada15</t>
         </is>
@@ -8296,7 +8296,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Sources: FBW  |  ID: e753e2a15c  |  SINGLE_SOURCE</t>
+          <t>Sources: FBW  |  ID: 1987_euro_champs  |  SINGLE_SOURCE</t>
         </is>
       </c>
     </row>
@@ -8345,35 +8345,35 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="n">
+      <c r="A5" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Jan-Olof Karlsson</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Jan-Olof Karlsson</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>NEW_PLAYER</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>4a11e53de5</t>
         </is>
       </c>
-      <c r="G5" s="17" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>6448a460-2f45-5a41-879d-f967d87e8a5c</t>
         </is>
@@ -8389,7 +8389,7 @@
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Location: Golden, Colorado  |  Sources: FBW  |  ID: 8667de3590  |  CONFIRMED_MULTI_SOURCE</t>
+          <t>Location: Golden, Colorado  |  Sources: FBW  |  ID: 1987_worlds_golden  |  CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
     </row>
@@ -8964,35 +8964,35 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="n">
+      <c r="A29" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>Doug Little</t>
         </is>
       </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>Doug Little</t>
         </is>
       </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>NEW_PLAYER</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
         <is>
           <t>2373ad3c27</t>
         </is>
       </c>
-      <c r="G29" s="17" t="inlineStr">
+      <c r="G29" s="16" t="inlineStr">
         <is>
           <t>d86e1aad-2058-5773-95eb-c5fd05217112</t>
         </is>
@@ -9490,35 +9490,35 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="17" t="n">
+      <c r="A47" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B47" s="17" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>Ken Eldrick</t>
         </is>
       </c>
-      <c r="C47" s="17" t="inlineStr">
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>Ken Eldrick</t>
         </is>
       </c>
-      <c r="D47" s="17" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>NEW_PLAYER</t>
         </is>
       </c>
-      <c r="E47" s="17" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F47" s="17" t="inlineStr">
+      <c r="E47" s="16" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
         <is>
           <t>2373ad3c27</t>
         </is>
       </c>
-      <c r="G47" s="17" t="inlineStr">
+      <c r="G47" s="16" t="inlineStr">
         <is>
           <t>03bcdedb-b187-5ef3-ba2d-e371c1cada15</t>
         </is>
@@ -10138,7 +10138,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Location: Chicago, Illinois  |  Sources: FBW  |  ID: 7f20a87202  |  SINGLE_SOURCE</t>
+          <t>Location: Chicago, Illinois  |  Sources: FBW  |  ID: 1988_us_nationals  |  SINGLE_SOURCE</t>
         </is>
       </c>
     </row>
@@ -10187,35 +10187,35 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="n">
+      <c r="A5" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Ken Eldrick</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Ken Eldrick</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>NEW_PLAYER</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>9f5e7b1351</t>
         </is>
       </c>
-      <c r="G5" s="17" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>03bcdedb-b187-5ef3-ba2d-e371c1cada15</t>
         </is>
@@ -10231,7 +10231,7 @@
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Location: Golden, Colorado  |  Sources: FBW  |  ID: d272be24f7  |  CONFIRMED_MULTI_SOURCE</t>
+          <t>Location: Golden, Colorado  |  Sources: FBW  |  ID: 1988_worlds_golden  |  CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
     </row>
@@ -11332,35 +11332,35 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="17" t="n">
+      <c r="A47" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B47" s="17" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>Ken Eldrick</t>
         </is>
       </c>
-      <c r="C47" s="17" t="inlineStr">
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>Ken Eldrick</t>
         </is>
       </c>
-      <c r="D47" s="17" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>NEW_PLAYER</t>
         </is>
       </c>
-      <c r="E47" s="17" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F47" s="17" t="inlineStr">
+      <c r="E47" s="16" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
         <is>
           <t>a325895452</t>
         </is>
       </c>
-      <c r="G47" s="17" t="inlineStr">
+      <c r="G47" s="16" t="inlineStr">
         <is>
           <t>03bcdedb-b187-5ef3-ba2d-e371c1cada15</t>
         </is>
@@ -11945,7 +11945,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Location: Golden, Colorado  |  Sources: FBW|IFAB  |  ID: 334c632f6e  |  CONFIRMED_MULTI_SOURCE</t>
+          <t>Location: Golden, Colorado  |  Sources: FBW|IFAB  |  ID: 1989_worlds_golden  |  CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
     </row>
@@ -12967,35 +12967,35 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="n">
+      <c r="A38" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>Ken Eldrick</t>
         </is>
       </c>
-      <c r="C38" s="17" t="inlineStr">
+      <c r="C38" s="16" t="inlineStr">
         <is>
           <t>Ken Eldrick</t>
         </is>
       </c>
-      <c r="D38" s="17" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>NEW_PLAYER</t>
         </is>
       </c>
-      <c r="E38" s="17" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
         <is>
           <t>8c04e22a55</t>
         </is>
       </c>
-      <c r="G38" s="17" t="inlineStr">
+      <c r="G38" s="16" t="inlineStr">
         <is>
           <t>03bcdedb-b187-5ef3-ba2d-e371c1cada15</t>
         </is>
@@ -13576,7 +13576,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Sources: FBW  |  ID: 15782bd1d5  |  SINGLE_SOURCE</t>
+          <t>Sources: FBW  |  ID: 1990_worlds  |  SINGLE_SOURCE</t>
         </is>
       </c>
     </row>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>Mag Hughes / Steve Femmel</t>
+          <t>Mag Hughes / Steve Fennell</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
@@ -14529,7 +14529,7 @@
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>Steve Femmel</t>
+          <t>Steve Fennell</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
@@ -15127,7 +15127,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Sources: FBW  |  ID: 76340820ba  |  SINGLE_SOURCE</t>
+          <t>Sources: FBW  |  ID: 1991_worlds  |  SINGLE_SOURCE</t>
         </is>
       </c>
     </row>
@@ -15633,7 +15633,7 @@
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>Mag Hughes / Steve Femmel</t>
+          <t>Mag Hughes / Steve Fennell</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
@@ -16010,7 +16010,7 @@
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Steve Femmel</t>
+          <t>Steve Fennell</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
@@ -16678,7 +16678,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Sources: FBW  |  ID: 07e711d92a  |  SINGLE_SOURCE</t>
+          <t>Sources: FBW  |  ID: 1992_worlds  |  SINGLE_SOURCE</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Steve Femmel</t>
+          <t>Steve Fennell</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
@@ -17184,7 +17184,7 @@
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>Mag Hughes / Steve Femmel</t>
+          <t>Mag Hughes / Steve Fennell</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
@@ -17561,7 +17561,7 @@
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Steve Femmel</t>
+          <t>Steve Fennell</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
@@ -18229,7 +18229,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Sources: FBW  |  ID: e04899bee1  |  SINGLE_SOURCE</t>
+          <t>Sources: FBW  |  ID: 1993_worlds  |  SINGLE_SOURCE</t>
         </is>
       </c>
     </row>
@@ -18288,7 +18288,7 @@
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Steve Femmel</t>
+          <t>Steve Fennell</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
@@ -18665,7 +18665,7 @@
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Dave Robinson / Steve Femmel</t>
+          <t>Dave Robinson / Steve Fennell</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
@@ -19023,35 +19023,35 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="n">
+      <c r="A30" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>Torgeir Rygh</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>Torgeir Rygh</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>NEW_PLAYER</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>392abf2112</t>
         </is>
       </c>
-      <c r="G30" s="17" t="inlineStr">
+      <c r="G30" s="16" t="inlineStr">
         <is>
           <t>42b5c8be-9cb5-5b3b-b167-13fd86b35ca4</t>
         </is>
@@ -19112,7 +19112,7 @@
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Steve Femmel</t>
+          <t>Steve Fennell</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
@@ -19321,35 +19321,35 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="n">
+      <c r="A40" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B40" s="17" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>Torgeir Rygh / Sindre Madsen</t>
         </is>
       </c>
-      <c r="C40" s="17" t="inlineStr">
+      <c r="C40" s="16" t="inlineStr">
         <is>
           <t>Torgeir Rygh / Sindre Madsen</t>
         </is>
       </c>
-      <c r="D40" s="17" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>NEW_PLAYER / NEW_PLAYER</t>
         </is>
       </c>
-      <c r="E40" s="17" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F40" s="17" t="inlineStr">
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
         <is>
           <t>392abf2112</t>
         </is>
       </c>
-      <c r="G40" s="17" t="inlineStr">
+      <c r="G40" s="16" t="inlineStr">
         <is>
           <t>42b5c8be-9cb5-5b3b-b167-13fd86b35ca4 / e0682f82-69f2-5395-bf80-1f7c9a2e2cad</t>
         </is>
@@ -19780,7 +19780,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Location: Palo Alto, California  |  Sources: FBW|IFAB  |  ID: b9d35c4646  |  CONFIRMED_MULTI_SOURCE</t>
+          <t>Location: Palo Alto, California  |  Sources: FBW|IFAB  |  ID: 1994_worlds_palo_alto  |  CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
     </row>
@@ -20216,7 +20216,7 @@
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Dave Robinson / Steve Femmel</t>
+          <t>Dave Robinson / Steve Fennell</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
@@ -20574,35 +20574,35 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="n">
+      <c r="A30" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>Torgeir Rygh</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>Torgeir Rygh</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>NEW_PLAYER</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>dbe602bdaa</t>
         </is>
       </c>
-      <c r="G30" s="17" t="inlineStr">
+      <c r="G30" s="16" t="inlineStr">
         <is>
           <t>42b5c8be-9cb5-5b3b-b167-13fd86b35ca4</t>
         </is>
@@ -20698,7 +20698,7 @@
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>Steve Femmel</t>
+          <t>Steve Fennell</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
@@ -20812,7 +20812,7 @@
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Steve Femmel</t>
+          <t>Steve Fennell</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
@@ -21597,7 +21597,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Sources: FBW  |  ID: 1faddf6c05  |  SINGLE_SOURCE</t>
+          <t>Sources: FBW  |  ID: 1995_worlds  |  SINGLE_SOURCE</t>
         </is>
       </c>
     </row>
@@ -21656,7 +21656,7 @@
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Steve Femmel</t>
+          <t>Steve Fennell</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
@@ -22033,7 +22033,7 @@
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Dave Robinson / Steve Femmel</t>
+          <t>Dave Robinson / Steve Fennell</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
@@ -22391,35 +22391,35 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="n">
+      <c r="A30" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>Torgeir Rygh</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>Torgeir Rygh</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>NEW_PLAYER</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>1ab305536b</t>
         </is>
       </c>
-      <c r="G30" s="17" t="inlineStr">
+      <c r="G30" s="16" t="inlineStr">
         <is>
           <t>42b5c8be-9cb5-5b3b-b167-13fd86b35ca4</t>
         </is>
@@ -22480,7 +22480,7 @@
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Steve Femmel</t>
+          <t>Steve Fennell</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
@@ -23148,7 +23148,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Sources: FBW  |  ID: 6dc440629d  |  SINGLE_SOURCE</t>
+          <t>Sources: FBW  |  ID: 1996_worlds  |  SINGLE_SOURCE</t>
         </is>
       </c>
     </row>
@@ -23207,7 +23207,7 @@
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Steve Femmel</t>
+          <t>Steve Fennell</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
@@ -23584,7 +23584,7 @@
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Dave Robinson / Steve Femmel</t>
+          <t>Dave Robinson / Steve Fennell</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
@@ -24031,7 +24031,7 @@
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Steve Femmel</t>
+          <t>Steve Fennell</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
@@ -24704,23 +24704,23 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>SINGLE_SOURCE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -24743,27 +24743,27 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>MATCHED</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1086</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>AUTOACCEPTED</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>NEW_PLAYER</t>
         </is>
@@ -24779,7 +24779,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -24882,12 +24882,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
@@ -24946,7 +24946,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>069f7909e7</t>
+          <t>1980_worlds</t>
         </is>
       </c>
       <c r="B2" s="8" t="n">
@@ -24954,27 +24954,27 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>1980 Mike Marshall Memorial</t>
+          <t>1980 NHSA (Mike Marshall Memorial)</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr"/>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>NHSA_NATIONALS</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>FBW</t>
+          <t>FBW|OLD_RESULTS</t>
         </is>
       </c>
       <c r="G2" s="9" t="inlineStr">
         <is>
-          <t>SINGLE_SOURCE</t>
+          <t>CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
       <c r="H2" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I2" s="8" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bb975bff1d</t>
+          <t>1980_worlds_clackamas</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -24993,27 +24993,31 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1980 NHSA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>1980 National / World Footbag Championships</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Clackamas, Oregon</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>NHSA_NATIONALS</t>
+          <t>WORLD_CHAMPIONSHIPS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>OLD_RESULTS</t>
+          <t>FBW|IFAB</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>SINGLE_SOURCE</t>
+          <t>CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -25024,39 +25028,35 @@
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>8396ba09ac</t>
+          <t>1981_worlds</t>
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>1980 National Footbag Championships</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Clackamas, Oregon</t>
-        </is>
-      </c>
+          <t>1981 NHSA (Mike Marshall Memorial)</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr"/>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>US_NATIONALS</t>
+          <t>NHSA_NATIONALS</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>FBW</t>
+          <t>FBW|OLD_RESULTS</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>SINGLE_SOURCE</t>
+          <t>CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
       <c r="H4" s="8" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
@@ -25067,15 +25067,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5c386b7dea</t>
+          <t>1981_worlds_portland</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1980 World Footbag Championships</t>
+          <t>1981 World Footbag Championships</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -25090,16 +25090,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IFAB</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>SINGLE_SOURCE</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -25110,35 +25110,35 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>bc88796233</t>
+          <t>1982_worlds</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>1981 Mike Marshall Memorial</t>
+          <t>1982 NHSA</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>NHSA_NATIONALS</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>FBW</t>
+          <t>FBW|OLD_RESULTS</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>SINGLE_SOURCE</t>
+          <t>CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
       <c r="H6" s="8" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
@@ -25149,35 +25149,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>b9540daaab</t>
+          <t>1982_western_regionals</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1981 NHSA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>1982 Western Regionals</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NHSA_NATIONALS</t>
+          <t>US_REGIONALS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OLD_RESULTS</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>SINGLE_SOURCE</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -25188,15 +25192,15 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>af9e865ed5</t>
+          <t>1982_worlds_portland</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>1981 World Footbag Championships</t>
+          <t>1982 World Footbag Championships</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -25214,13 +25218,13 @@
           <t>FBW</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>SINGLE_SOURCE</t>
         </is>
       </c>
       <c r="H8" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
@@ -25231,15 +25235,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1e36e7ca92</t>
+          <t>1983_worlds_nhsa</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1982 NHSA</t>
+          <t>1983 NHSA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -25253,13 +25257,13 @@
           <t>FBW|OLD_RESULTS</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -25270,25 +25274,25 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>e41e20722d</t>
+          <t>1983_oregon_state</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>1982 Western Regionals</t>
+          <t>1983 Oregon State Championships</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Oregon</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>US_REGIONALS</t>
+          <t>STATE_CHAMPIONSHIPS</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -25296,7 +25300,7 @@
           <t>FBW</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>SINGLE_SOURCE</t>
         </is>
@@ -25313,39 +25317,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>f771c4ef26</t>
+          <t>1983_worlds_wfa</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1982 World Footbag Championships</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Portland, Oregon</t>
-        </is>
-      </c>
+          <t>1983 WFA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>WORLD_CHAMPIONSHIPS</t>
+          <t>WFA_NATIONALS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FBW</t>
+          <t>FBW|OLD_RESULTS</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>SINGLE_SOURCE</t>
+          <t>CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>76498d51d2</t>
+          <t>1983_worlds_portland</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
@@ -25364,27 +25364,31 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>1983 NHSA</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr"/>
+          <t>1983 World Footbag Championships</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Portland, Oregon</t>
+        </is>
+      </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>NHSA_NATIONALS</t>
+          <t>WORLD_CHAMPIONSHIPS</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>FBW|OLD_RESULTS</t>
+          <t>FBW</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>CONFIRMED_MULTI_SOURCE</t>
+          <t>SINGLE_SOURCE</t>
         </is>
       </c>
       <c r="H12" s="8" t="n">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
@@ -25395,39 +25399,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0a43031545</t>
+          <t>1984_worlds</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1983 Oregon State Championships</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Oregon</t>
-        </is>
-      </c>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>STATE_CHAMPIONSHIPS</t>
+          <t>WORLD_CHAMPIONSHIPS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FBW</t>
+          <t>FBW|OLD_RESULTS</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>SINGLE_SOURCE</t>
+          <t>CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -25438,35 +25438,35 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>00659874b9</t>
+          <t>1984_euro_champs</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>1983 WFA</t>
+          <t>1984 European Footbag Championships</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr"/>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>WFA_NATIONALS</t>
+          <t>EURO_CHAMPIONSHIPS</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>FBW|OLD_RESULTS</t>
+          <t>FBW</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>CONFIRMED_MULTI_SOURCE</t>
+          <t>SINGLE_SOURCE</t>
         </is>
       </c>
       <c r="H14" s="8" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
@@ -25477,39 +25477,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>76ff377548</t>
+          <t>1984_wfa_nationals</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1983 World Footbag Championships</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Portland, Oregon</t>
-        </is>
-      </c>
+          <t>1984 WFA National Championships</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>WORLD_CHAMPIONSHIPS</t>
+          <t>WFA_NATIONALS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FBW</t>
+          <t>FBW|OLD_RESULTS</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>SINGLE_SOURCE</t>
+          <t>CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -25520,15 +25516,15 @@
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>6cd9e5b635</t>
+          <t>1985_worlds</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr"/>
@@ -25542,13 +25538,13 @@
           <t>FBW|OLD_RESULTS</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
       <c r="H16" s="8" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
@@ -25559,35 +25555,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>77aa0f8390</t>
+          <t>1985_wfa_nationals</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1984 European Footbag Championships</t>
+          <t>1985 WFA National Championships</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EURO_CHAMPIONSHIPS</t>
+          <t>WFA_NATIONALS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FBW</t>
+          <t>FBW|OLD_RESULTS</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>SINGLE_SOURCE</t>
+          <t>CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -25598,21 +25594,25 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>0e1499ab21</t>
+          <t>1986_worlds_golden</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>1984 WFA National Championships</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr"/>
+          <t>1986 WFA World Championships</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Golden, Colorado</t>
+        </is>
+      </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>WFA_NATIONALS</t>
+          <t>WFA_WORLD_CHAMPIONSHIPS</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -25620,13 +25620,13 @@
           <t>FBW|OLD_RESULTS</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
       <c r="H18" s="8" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
@@ -25637,35 +25637,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>88ab188635</t>
+          <t>1987_euro_champs</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1987 European Footbag Championships</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>WORLD_CHAMPIONSHIPS</t>
+          <t>EURO_CHAMPIONSHIPS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FBW|OLD_RESULTS</t>
+          <t>FBW</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>CONFIRMED_MULTI_SOURCE</t>
+          <t>SINGLE_SOURCE</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -25676,35 +25676,39 @@
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>1c74083104</t>
+          <t>1987_worlds_golden</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>1985 WFA National Championships</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr"/>
+          <t>1987 WFA World Championships</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Golden, Colorado</t>
+        </is>
+      </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>WFA_NATIONALS</t>
+          <t>WFA_WORLD_CHAMPIONSHIPS</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>FBW|OLD_RESULTS</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
       <c r="H20" s="8" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
@@ -25715,39 +25719,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>b4b6a194e2</t>
+          <t>1988_us_nationals</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1986 WFA World Championships</t>
+          <t>1988 U.S. National Footbag Championships</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Golden, Colorado</t>
+          <t>Chicago, Illinois</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>WFA_WORLD_CHAMPIONSHIPS</t>
+          <t>US_NATIONALS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FBW|OLD_RESULTS</t>
+          <t>FBW</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>CONFIRMED_MULTI_SOURCE</t>
+          <t>SINGLE_SOURCE</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -25758,21 +25762,25 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>e753e2a15c</t>
+          <t>1988_worlds_golden</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>1987 European Footbag Championships</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr"/>
+          <t>1988 WFA World Championships</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Golden, Colorado</t>
+        </is>
+      </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>EURO_CHAMPIONSHIPS</t>
+          <t>WFA_WORLD_CHAMPIONSHIPS</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -25782,11 +25790,11 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>SINGLE_SOURCE</t>
+          <t>CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
       <c r="H22" s="8" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
@@ -25797,15 +25805,15 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8667de3590</t>
+          <t>1989_worlds_golden</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1987 WFA World Championships</t>
+          <t>1989 WFA World Championships</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -25820,16 +25828,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
+          <t>FBW|IFAB</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -25840,25 +25848,21 @@
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>7f20a87202</t>
+          <t>1990_worlds</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>1988 U.S. National Footbag Championships</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Chicago, Illinois</t>
-        </is>
-      </c>
+          <t>1990 WFA World Championships</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr"/>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>US_NATIONALS</t>
+          <t>WFA_WORLD_CHAMPIONSHIPS</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -25866,13 +25870,13 @@
           <t>FBW</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>SINGLE_SOURCE</t>
         </is>
       </c>
       <c r="H24" s="8" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
@@ -25883,22 +25887,18 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>d272be24f7</t>
+          <t>1991_worlds</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1988</v>
+        <v>1991</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1988 WFA World Championships</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Golden, Colorado</t>
-        </is>
-      </c>
+          <t>1991 WFA World Championships</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>WFA_WORLD_CHAMPIONSHIPS</t>
@@ -25911,11 +25911,11 @@
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>CONFIRMED_MULTI_SOURCE</t>
+          <t>SINGLE_SOURCE</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -25926,22 +25926,18 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>334c632f6e</t>
+          <t>1992_worlds</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>1989</v>
+        <v>1992</v>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>1989 WFA World Championships</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Golden, Colorado</t>
-        </is>
-      </c>
+          <t>1992 WFA World Championships</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr"/>
       <c r="E26" s="8" t="inlineStr">
         <is>
           <t>WFA_WORLD_CHAMPIONSHIPS</t>
@@ -25949,16 +25945,16 @@
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>FBW|IFAB</t>
+          <t>FBW</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>CONFIRMED_MULTI_SOURCE</t>
+          <t>SINGLE_SOURCE</t>
         </is>
       </c>
       <c r="H26" s="8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
@@ -25969,21 +25965,21 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>15782bd1d5</t>
+          <t>1993_worlds</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1990</v>
+        <v>1993</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1990 WFA World Championships</t>
+          <t>1993 IFAB World Championships</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>WFA_WORLD_CHAMPIONSHIPS</t>
+          <t>IFAB_WORLD_CHAMPIONSHIPS</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -25991,7 +25987,7 @@
           <t>FBW</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G27" s="10" t="inlineStr">
         <is>
           <t>SINGLE_SOURCE</t>
         </is>
@@ -26008,35 +26004,39 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>76340820ba</t>
+          <t>1994_worlds_palo_alto</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>1991</v>
+        <v>1994</v>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>1991 WFA World Championships</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr"/>
+          <t>1994 IFAB World Championships</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Palo Alto, California</t>
+        </is>
+      </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>WFA_WORLD_CHAMPIONSHIPS</t>
+          <t>IFAB_WORLD_CHAMPIONSHIPS</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>FBW</t>
+          <t>FBW|IFAB</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>SINGLE_SOURCE</t>
+          <t>CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
       <c r="H28" s="8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
@@ -26047,21 +26047,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07e711d92a</t>
+          <t>1995_worlds</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1992</v>
+        <v>1995</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1992 WFA World Championships</t>
+          <t>1995 IFAB World Championships</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>WFA_WORLD_CHAMPIONSHIPS</t>
+          <t>IFAB_WORLD_CHAMPIONSHIPS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -26069,7 +26069,7 @@
           <t>FBW</t>
         </is>
       </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="G29" s="10" t="inlineStr">
         <is>
           <t>SINGLE_SOURCE</t>
         </is>
@@ -26086,15 +26086,15 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>e04899bee1</t>
+          <t>1996_worlds</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>1993</v>
+        <v>1996</v>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>1993 IFAB World Championships</t>
+          <t>1996 IFAB World Championships</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr"/>
@@ -26108,7 +26108,7 @@
           <t>FBW</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>SINGLE_SOURCE</t>
         </is>
@@ -26117,127 +26117,6 @@
         <v>29</v>
       </c>
       <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>b9d35c4646</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1994</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1994 IFAB World Championships</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Palo Alto, California</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>IFAB_WORLD_CHAMPIONSHIPS</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>FBW|IFAB</t>
-        </is>
-      </c>
-      <c r="G31" s="10" t="inlineStr">
-        <is>
-          <t>CONFIRMED_MULTI_SOURCE</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>30</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>1faddf6c05</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="n">
-        <v>1995</v>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>1995 IFAB World Championships</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr"/>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>IFAB_WORLD_CHAMPIONSHIPS</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="H32" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>6dc440629d</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1996</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1996 IFAB World Championships</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>IFAB_WORLD_CHAMPIONSHIPS</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>SINGLE_SOURCE</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>29</v>
-      </c>
-      <c r="I33" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
@@ -26399,7 +26278,7 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doubles Consecutive </t>
+          <t>Open Sgls Consecutiv</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -26465,11 +26344,11 @@
         </is>
       </c>
       <c r="E6" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Mixed Dbls Net</t>
+          <t>Doubles Net</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -26710,7 +26589,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mixed Dbls Net</t>
+          <t>Women's Dbls Net</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -26745,7 +26624,7 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>Advanced Doubles Net</t>
+          <t>Golf</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
@@ -26815,7 +26694,7 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>Mixed Dbls Net</t>
+          <t>Women's Doubles Cons</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
@@ -26846,7 +26725,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -26881,7 +26760,7 @@
         </is>
       </c>
       <c r="E18" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
@@ -26920,7 +26799,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mixed Dbls Net</t>
+          <t>Open Sgls Net</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -27161,7 +27040,7 @@
         </is>
       </c>
       <c r="E26" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
@@ -27231,7 +27110,7 @@
         </is>
       </c>
       <c r="E28" s="8" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
       <c r="G28" s="8" t="inlineStr">
@@ -27468,7 +27347,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Singles</t>
+          <t xml:space="preserve">Doubles Consecutive </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -27499,11 +27378,11 @@
         </is>
       </c>
       <c r="E36" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>Women's Dbls Net</t>
+          <t>Women's Doubles Net</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
@@ -27573,7 +27452,7 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>Mixed Doubles Net</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
@@ -27604,11 +27483,11 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mixed Doubles Net</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -27643,7 +27522,7 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>Advanced Doubles Net</t>
+          <t xml:space="preserve">Doubles Consecutive </t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
@@ -27678,7 +27557,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Women's Doubles Net</t>
+          <t>Women's Doubles Cons</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -27814,11 +27693,11 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Open Singles Net</t>
+          <t>Doubles Net</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -27888,7 +27767,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mixed Dbls Net</t>
+          <t>Women's Doubles Net</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -27919,11 +27798,11 @@
         </is>
       </c>
       <c r="E48" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>Women's Sgls Consecu</t>
+          <t>Team Consecutive Kic</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
@@ -28063,7 +27942,7 @@
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>Open Singles Net</t>
+          <t>Open Doubles Net</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
@@ -28129,7 +28008,7 @@
         </is>
       </c>
       <c r="E54" s="8" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
@@ -28343,7 +28222,7 @@
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>Women's Golf</t>
+          <t>Women's Dbls Net</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
@@ -28374,11 +28253,11 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mixed Dbls Net</t>
+          <t>Women's Dbls Net</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -28409,11 +28288,11 @@
         </is>
       </c>
       <c r="E62" s="8" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>Mixed Doubles Net</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
@@ -28448,7 +28327,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Women's Singles Cons</t>
+          <t>Women's Doubles Cons</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -28549,16 +28428,16 @@
         </is>
       </c>
       <c r="E66" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>Intermediate Singles</t>
+          <t>Doubles Net</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>Max Smith; Max Smith Jr.</t>
+          <t>Max Smith</t>
         </is>
       </c>
     </row>
@@ -28584,11 +28463,11 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doubles Consecutive </t>
+          <t>Golf</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -28724,16 +28603,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Women's Dbls Net</t>
+          <t>Women's Doubles Net</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Misty Helme; Misty Helms</t>
+          <t>Misty Helms</t>
         </is>
       </c>
     </row>
@@ -28763,7 +28642,7 @@
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>Mixed Dbls Net</t>
+          <t>Women's Doubles Cons</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
@@ -28798,7 +28677,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Open Sgls Consecutiv</t>
+          <t xml:space="preserve">Doubles Consecutive </t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -29004,7 +28883,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Open Sgls Consecutiv</t>
+          <t>Open Freestyle</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -29035,7 +28914,7 @@
         </is>
       </c>
       <c r="E80" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
@@ -29074,7 +28953,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Team Freestyle</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -29109,7 +28988,7 @@
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>Women's Freestyle</t>
+          <t>Women's Doubles One-</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
@@ -29301,7 +29180,7 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Steve Femmel</t>
+          <t>Steve Fennell</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
@@ -29319,12 +29198,12 @@
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>Open Singles Net</t>
+          <t>Open Sgls Net</t>
         </is>
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>Steve Femmel; Steve Fennell</t>
+          <t>Steve Fennell</t>
         </is>
       </c>
     </row>
@@ -29389,7 +29268,7 @@
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>Mixed Dbls Net</t>
+          <t>Women's Team Freesty</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
@@ -29494,7 +29373,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Golf</t>
+          <t>Open Golf</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -29599,7 +29478,7 @@
       </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
-          <t>Golf</t>
+          <t>Open Golf</t>
         </is>
       </c>
       <c r="G96" s="8" t="inlineStr">
@@ -29669,7 +29548,7 @@
       </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
-          <t>Mixed Dbls Net</t>
+          <t>Women's Doubles Cons</t>
         </is>
       </c>
       <c r="G98" s="8" t="inlineStr">
@@ -29704,7 +29583,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Women's Golf</t>
+          <t>Women's Dbls Net</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -29739,7 +29618,7 @@
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
-          <t>Women's Golf</t>
+          <t>Women's Doubles Cons</t>
         </is>
       </c>
       <c r="G100" s="8" t="inlineStr">
@@ -29770,7 +29649,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -29809,7 +29688,7 @@
       </c>
       <c r="F102" s="8" t="inlineStr">
         <is>
-          <t>Team Freestyle</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="G102" s="8" t="inlineStr">
@@ -29829,7 +29708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -29844,21 +29723,21 @@
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>1980 Mike Marshall Memorial</t>
+          <t>1980 NHSA (Mike Marshall Memorial)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Sources: FBW  |  ID: 069f7909e7  |  SINGLE_SOURCE</t>
+          <t>Sources: FBW|OLD_RESULTS  |  ID: 1980_worlds  |  CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>Open Dbls Consecutive</t>
+          <t>Doubles Consecutive Kicks</t>
         </is>
       </c>
     </row>
@@ -29905,7 +29784,7 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Kenny Shults / Mike Harding</t>
+          <t>Ken Shults / Mike Harding</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
@@ -29920,12 +29799,12 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>FBW</t>
+          <t>OLD_RESULTS</t>
         </is>
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>005cf9782a</t>
+          <t>b34e90fe3d</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -29937,7 +29816,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Open Dbls Net</t>
+          <t>Doubles Net</t>
         </is>
       </c>
     </row>
@@ -29984,7 +29863,7 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>John Stalberger / Max Smith Jr.</t>
+          <t>John Stalberger / Max Smith</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -29994,17 +29873,17 @@
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>MATCHED / AUTOACCEPTED</t>
+          <t>MATCHED / MATCHED</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>FBW</t>
+          <t>OLD_RESULTS</t>
         </is>
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>005cf9782a</t>
+          <t>b34e90fe3d</t>
         </is>
       </c>
       <c r="G8" s="15" t="inlineStr">
@@ -30019,12 +29898,12 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Mag Hughes / Walt Mason</t>
+          <t>Walt Mason / Mag Hughes</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>Mag Hughes / Walt Mason</t>
+          <t>Walt Mason / Mag Hughes</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
@@ -30034,17 +29913,17 @@
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>FBW</t>
+          <t>OLD_RESULTS</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
-          <t>005cf9782a</t>
+          <t>b34e90fe3d</t>
         </is>
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>ca63a7da-a00a-5a83-ae43-2e17b5758fc8 / c0592850-ae68-5b8b-aaf2-2741b8bdc51d</t>
+          <t>c0592850-ae68-5b8b-aaf2-2741b8bdc51d / ca63a7da-a00a-5a83-ae43-2e17b5758fc8</t>
         </is>
       </c>
     </row>
@@ -30069,12 +29948,12 @@
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>FBW</t>
+          <t>OLD_RESULTS</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>005cf9782a</t>
+          <t>b34e90fe3d</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
@@ -30086,7 +29965,7 @@
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Open Sgls Consecutive</t>
+          <t>Singles Consecutive Kicks</t>
         </is>
       </c>
     </row>
@@ -30133,7 +30012,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>Kenny Shults</t>
+          <t>Ken Shults</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
@@ -30148,12 +30027,12 @@
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>FBW</t>
+          <t>OLD_RESULTS</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>005cf9782a</t>
+          <t>b34e90fe3d</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr">
@@ -30165,7 +30044,7 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>Open Sgls Net</t>
+          <t>Singles Net</t>
         </is>
       </c>
     </row>
@@ -30227,12 +30106,12 @@
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>FBW</t>
+          <t>OLD_RESULTS</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
         <is>
-          <t>005cf9782a</t>
+          <t>b34e90fe3d</t>
         </is>
       </c>
       <c r="G16" s="15" t="inlineStr">
@@ -30262,12 +30141,12 @@
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>FBW</t>
+          <t>OLD_RESULTS</t>
         </is>
       </c>
       <c r="F17" s="15" t="inlineStr">
         <is>
-          <t>005cf9782a</t>
+          <t>b34e90fe3d</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr">
@@ -30282,7 +30161,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>Kenny Shults</t>
+          <t>Ken Shults</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
@@ -30297,12 +30176,12 @@
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>FBW</t>
+          <t>OLD_RESULTS</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
         <is>
-          <t>005cf9782a</t>
+          <t>b34e90fe3d</t>
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr">
@@ -30311,71 +30190,24 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>Women's Dbls Net</t>
-        </is>
-      </c>
-    </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>Place</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>Player(s)</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>Canon Name</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E20" s="14" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>Person ID</t>
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>1980 National / World Footbag Championships</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr"/>
-      <c r="B21" s="16" t="inlineStr"/>
-      <c r="C21" s="16" t="inlineStr"/>
-      <c r="D21" s="16" t="inlineStr"/>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>005cf9782a</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr"/>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Location: Clackamas, Oregon  |  Sources: FBW|IFAB  |  ID: 1980_worlds_clackamas  |  CONFIRMED_MULTI_SOURCE</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>Women's Sgls Net</t>
+          <t>Open Singles</t>
         </is>
       </c>
     </row>
@@ -30417,735 +30249,86 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="inlineStr"/>
-      <c r="B24" s="16" t="inlineStr"/>
-      <c r="C24" s="16" t="inlineStr"/>
-      <c r="D24" s="16" t="inlineStr"/>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>005cf9782a</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>1980 NHSA</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>Sources: OLD_RESULTS  |  ID: bb975bff1d  |  SINGLE_SOURCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>Doubles Consecutive Kicks</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
-        <is>
-          <t>Place</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>Player(s)</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>Canon Name</t>
-        </is>
-      </c>
-      <c r="D29" s="14" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="G29" s="14" t="inlineStr">
-        <is>
-          <t>Person ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="n">
+      <c r="A24" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>Ken Shults / Mike Harding</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
-        <is>
-          <t>Kenneth Shults / Mike Harding</t>
-        </is>
-      </c>
-      <c r="D30" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED / MATCHED</t>
-        </is>
-      </c>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
-          <t>OLD_RESULTS</t>
-        </is>
-      </c>
-      <c r="F30" s="15" t="inlineStr">
-        <is>
-          <t>b34e90fe3d</t>
-        </is>
-      </c>
-      <c r="G30" s="15" t="inlineStr">
-        <is>
-          <t>2a6a7c9e-1d8a-4f9a-a8f5-6f3a3c1e9b0f / d75b5871-83c1-5284-b09d-a5eb5d4377dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>Doubles Net</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>Place</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>Player(s)</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="inlineStr">
-        <is>
-          <t>Canon Name</t>
-        </is>
-      </c>
-      <c r="D32" s="14" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E32" s="14" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>Person ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>John Stalberger / Max Smith</t>
-        </is>
-      </c>
-      <c r="C33" s="15" t="inlineStr">
-        <is>
-          <t>John Stalberger / Max Smith</t>
-        </is>
-      </c>
-      <c r="D33" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED / MATCHED</t>
-        </is>
-      </c>
-      <c r="E33" s="15" t="inlineStr">
-        <is>
-          <t>OLD_RESULTS</t>
-        </is>
-      </c>
-      <c r="F33" s="15" t="inlineStr">
-        <is>
-          <t>b34e90fe3d</t>
-        </is>
-      </c>
-      <c r="G33" s="15" t="inlineStr">
-        <is>
-          <t>8f420eba-d663-5f06-b0f4-b62bf7550f80 / 95fb4def-7ff2-5c9c-8de5-1b97d0e13756</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="n">
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>John Stalberger</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>John Stalberger</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>a6acc8449b</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>8f420eba-d663-5f06-b0f4-b62bf7550f80</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>Walt Mason / Mag Hughes</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="inlineStr">
-        <is>
-          <t>Walt Mason / Mag Hughes</t>
-        </is>
-      </c>
-      <c r="D34" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED / MATCHED</t>
-        </is>
-      </c>
-      <c r="E34" s="15" t="inlineStr">
-        <is>
-          <t>OLD_RESULTS</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="inlineStr">
-        <is>
-          <t>b34e90fe3d</t>
-        </is>
-      </c>
-      <c r="G34" s="15" t="inlineStr">
-        <is>
-          <t>c0592850-ae68-5b8b-aaf2-2741b8bdc51d / ca63a7da-a00a-5a83-ae43-2e17b5758fc8</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B35" s="15" t="inlineStr">
-        <is>
-          <t>Gale Bigler / Dave Frazier</t>
-        </is>
-      </c>
-      <c r="C35" s="15" t="inlineStr">
-        <is>
-          <t>Gale Bigler / Dave Frazier</t>
-        </is>
-      </c>
-      <c r="D35" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED / MATCHED</t>
-        </is>
-      </c>
-      <c r="E35" s="15" t="inlineStr">
-        <is>
-          <t>OLD_RESULTS</t>
-        </is>
-      </c>
-      <c r="F35" s="15" t="inlineStr">
-        <is>
-          <t>b34e90fe3d</t>
-        </is>
-      </c>
-      <c r="G35" s="15" t="inlineStr">
-        <is>
-          <t>f06dc40d-e92e-5784-9269-cf25a77b450e / d00d203f-ac71-5ec1-ad7f-497a8f024c50</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
-        <is>
-          <t>Singles Consecutive Kicks</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>Place</t>
-        </is>
-      </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>Player(s)</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>Canon Name</t>
-        </is>
-      </c>
-      <c r="D37" s="14" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E37" s="14" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>Person ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B38" s="15" t="inlineStr">
-        <is>
-          <t>Ken Shults</t>
-        </is>
-      </c>
-      <c r="C38" s="15" t="inlineStr">
-        <is>
-          <t>Kenneth Shults</t>
-        </is>
-      </c>
-      <c r="D38" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
-          <t>OLD_RESULTS</t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="inlineStr">
-        <is>
-          <t>b34e90fe3d</t>
-        </is>
-      </c>
-      <c r="G38" s="15" t="inlineStr">
-        <is>
-          <t>2a6a7c9e-1d8a-4f9a-a8f5-6f3a3c1e9b0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="13" t="inlineStr">
-        <is>
-          <t>Singles Net</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="14" t="inlineStr">
-        <is>
-          <t>Place</t>
-        </is>
-      </c>
-      <c r="B40" s="14" t="inlineStr">
-        <is>
-          <t>Player(s)</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="inlineStr">
-        <is>
-          <t>Canon Name</t>
-        </is>
-      </c>
-      <c r="D40" s="14" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E40" s="14" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="F40" s="14" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>Person ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B41" s="15" t="inlineStr">
-        <is>
-          <t>John Stalberger</t>
-        </is>
-      </c>
-      <c r="C41" s="15" t="inlineStr">
-        <is>
-          <t>John Stalberger</t>
-        </is>
-      </c>
-      <c r="D41" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="E41" s="15" t="inlineStr">
-        <is>
-          <t>OLD_RESULTS</t>
-        </is>
-      </c>
-      <c r="F41" s="15" t="inlineStr">
-        <is>
-          <t>b34e90fe3d</t>
-        </is>
-      </c>
-      <c r="G41" s="15" t="inlineStr">
-        <is>
-          <t>8f420eba-d663-5f06-b0f4-b62bf7550f80</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B42" s="15" t="inlineStr">
-        <is>
-          <t>Walt Mason</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="inlineStr">
-        <is>
-          <t>Walt Mason</t>
-        </is>
-      </c>
-      <c r="D42" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="E42" s="15" t="inlineStr">
-        <is>
-          <t>OLD_RESULTS</t>
-        </is>
-      </c>
-      <c r="F42" s="15" t="inlineStr">
-        <is>
-          <t>b34e90fe3d</t>
-        </is>
-      </c>
-      <c r="G42" s="15" t="inlineStr">
-        <is>
-          <t>c0592850-ae68-5b8b-aaf2-2741b8bdc51d</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>Ken Shults</t>
-        </is>
-      </c>
-      <c r="C43" s="15" t="inlineStr">
-        <is>
-          <t>Kenneth Shults</t>
-        </is>
-      </c>
-      <c r="D43" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="E43" s="15" t="inlineStr">
-        <is>
-          <t>OLD_RESULTS</t>
-        </is>
-      </c>
-      <c r="F43" s="15" t="inlineStr">
-        <is>
-          <t>b34e90fe3d</t>
-        </is>
-      </c>
-      <c r="G43" s="15" t="inlineStr">
-        <is>
-          <t>2a6a7c9e-1d8a-4f9a-a8f5-6f3a3c1e9b0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>1980 National Footbag Championships</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>Location: Clackamas, Oregon  |  Sources: FBW  |  ID: 8396ba09ac  |  SINGLE_SOURCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="13" t="inlineStr">
-        <is>
-          <t>Open Singles</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="14" t="inlineStr">
-        <is>
-          <t>Place</t>
-        </is>
-      </c>
-      <c r="B48" s="14" t="inlineStr">
-        <is>
-          <t>Player(s)</t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="inlineStr">
-        <is>
-          <t>Canon Name</t>
-        </is>
-      </c>
-      <c r="D48" s="14" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E48" s="14" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="F48" s="14" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>Person ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>John Stalberger</t>
-        </is>
-      </c>
-      <c r="C49" s="15" t="inlineStr">
-        <is>
-          <t>John Stalberger</t>
-        </is>
-      </c>
-      <c r="D49" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="E49" s="15" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F49" s="15" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Ken Eldrick</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>Ken Eldrick</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>NEW_PLAYER</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
         <is>
           <t>a6acc8449b</t>
         </is>
       </c>
-      <c r="G49" s="15" t="inlineStr">
-        <is>
-          <t>8f420eba-d663-5f06-b0f4-b62bf7550f80</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B50" s="17" t="inlineStr">
-        <is>
-          <t>Ken Eldrick</t>
-        </is>
-      </c>
-      <c r="C50" s="17" t="inlineStr">
-        <is>
-          <t>Ken Eldrick</t>
-        </is>
-      </c>
-      <c r="D50" s="17" t="inlineStr">
-        <is>
-          <t>NEW_PLAYER</t>
-        </is>
-      </c>
-      <c r="E50" s="17" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F50" s="17" t="inlineStr">
-        <is>
-          <t>a6acc8449b</t>
-        </is>
-      </c>
-      <c r="G50" s="17" t="inlineStr">
+      <c r="G25" s="16" t="inlineStr">
         <is>
           <t>03bcdedb-b187-5ef3-ba2d-e371c1cada15</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>1980 World Footbag Championships</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="12" t="inlineStr">
-        <is>
-          <t>Location: Portland, Oregon  |  Sources: IFAB  |  ID: 5c386b7dea  |  SINGLE_SOURCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="13" t="inlineStr">
-        <is>
-          <t>Open Singles</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="14" t="inlineStr">
-        <is>
-          <t>Place</t>
-        </is>
-      </c>
-      <c r="B55" s="14" t="inlineStr">
-        <is>
-          <t>Player(s)</t>
-        </is>
-      </c>
-      <c r="C55" s="14" t="inlineStr">
-        <is>
-          <t>Canon Name</t>
-        </is>
-      </c>
-      <c r="D55" s="14" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E55" s="14" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="F55" s="14" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="G55" s="14" t="inlineStr">
-        <is>
-          <t>Person ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B56" s="15" t="inlineStr">
-        <is>
-          <t>John Stalberger</t>
-        </is>
-      </c>
-      <c r="C56" s="15" t="inlineStr">
-        <is>
-          <t>John Stalberger</t>
-        </is>
-      </c>
-      <c r="D56" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="E56" s="15" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F56" s="15" t="inlineStr">
-        <is>
-          <t>6f31575047</t>
-        </is>
-      </c>
-      <c r="G56" s="15" t="inlineStr">
-        <is>
-          <t>8f420eba-d663-5f06-b0f4-b62bf7550f80</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="9">
     <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A21:G21"/>
     <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A53:G53"/>
-    <mergeCell ref="A52:G52"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A54:G54"/>
-    <mergeCell ref="A46:G46"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A47:G47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -31157,7 +30340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -31172,21 +30355,21 @@
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>1981 Mike Marshall Memorial</t>
+          <t>1981 NHSA (Mike Marshall Memorial)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Sources: FBW  |  ID: bc88796233  |  SINGLE_SOURCE</t>
+          <t>Sources: FBW|OLD_RESULTS  |  ID: 1981_worlds  |  CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>Open Dbls Net</t>
+          <t>Doubles Net</t>
         </is>
       </c>
     </row>
@@ -31233,7 +30416,7 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Mag Hughes / Billy Hayne</t>
+          <t>Mag Hughes / Bill Hayne</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
@@ -31243,17 +30426,17 @@
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>MATCHED / AUTOACCEPTED</t>
+          <t>MATCHED / MATCHED</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>FBW</t>
+          <t>OLD_RESULTS</t>
         </is>
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>2a8ad0dbe8</t>
+          <t>db24e71377</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -31268,7 +30451,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>John Stalberger / Max Smith Jr.</t>
+          <t>John Stalberger / Max Smith</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
@@ -31278,17 +30461,17 @@
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>MATCHED / AUTOACCEPTED</t>
+          <t>MATCHED / MATCHED</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>FBW</t>
+          <t>OLD_RESULTS</t>
         </is>
       </c>
       <c r="F6" s="15" t="inlineStr">
         <is>
-          <t>2a8ad0dbe8</t>
+          <t>db24e71377</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -31303,7 +30486,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Kenny Shults / Walt Mason</t>
+          <t>Ken Shults / Walt Mason</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
@@ -31318,12 +30501,12 @@
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>FBW</t>
+          <t>OLD_RESULTS</t>
         </is>
       </c>
       <c r="F7" s="15" t="inlineStr">
         <is>
-          <t>2a8ad0dbe8</t>
+          <t>db24e71377</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
@@ -31335,7 +30518,7 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>Open Sgls Consecutive</t>
+          <t>Intermediate Doubles Net</t>
         </is>
       </c>
     </row>
@@ -31382,39 +30565,39 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Gary Laut</t>
+          <t>Mike Harding / Mark Daniels</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Gary Lautt</t>
+          <t>Mike Harding / Mark Daniels</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>AUTOACCEPTED</t>
+          <t>MATCHED / MATCHED</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>FBW</t>
+          <t>OLD_RESULTS</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>2a8ad0dbe8</t>
+          <t>db24e71377</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>66a5ee0b-abd2-5b24-9d53-5c4f6e3fee14</t>
+          <t>d75b5871-83c1-5284-b09d-a5eb5d4377dd / 33e83366-7b1e-5c4a-99a9-8eba0d3988ca</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Open Sgls Net</t>
+          <t>Intermediate Singles Consecutive Kicks</t>
         </is>
       </c>
     </row>
@@ -31461,483 +30644,566 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
+          <t>Max Smith</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Max Smith</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>OLD_RESULTS</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>db24e71377</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>95fb4def-7ff2-5c9c-8de5-1b97d0e13756</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Intermediate Singles Net</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Place</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Player(s)</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Canon Name</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>Source File</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>Person ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Mike Harding</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Mike Harding</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>OLD_RESULTS</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>db24e71377</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>d75b5871-83c1-5284-b09d-a5eb5d4377dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Singles Consecutive Kicks</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Place</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Player(s)</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Canon Name</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>Source File</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>Person ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Gary Lautt</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Gary Lautt</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>OLD_RESULTS</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>db24e71377</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>66a5ee0b-abd2-5b24-9d53-5c4f6e3fee14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Singles Net</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Place</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Player(s)</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>Canon Name</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>Source File</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>Person ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
           <t>John Stalberger</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>John Stalberger</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>MATCHED</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="inlineStr">
-        <is>
-          <t>2a8ad0dbe8</t>
-        </is>
-      </c>
-      <c r="G13" s="15" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>OLD_RESULTS</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>db24e71377</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
         <is>
           <t>8f420eba-d663-5f06-b0f4-b62bf7550f80</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>Kenny Shults</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>Kenneth Shults</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F14" s="15" t="inlineStr">
-        <is>
-          <t>2a8ad0dbe8</t>
-        </is>
-      </c>
-      <c r="G14" s="15" t="inlineStr">
-        <is>
-          <t>2a6a7c9e-1d8a-4f9a-a8f5-6f3a3c1e9b0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>Dave Hill</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Dave Hill</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F15" s="15" t="inlineStr">
-        <is>
-          <t>2a8ad0dbe8</t>
-        </is>
-      </c>
-      <c r="G15" s="15" t="inlineStr">
-        <is>
-          <t>5cb79fb4-ab20-558f-b4a2-e7206c9f22df</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Open Team Consecutive</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>Place</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>Player(s)</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>Canon Name</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="F17" s="14" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>Person ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>Gary Laut / Jim Caveney / Kalia Klaban</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>Gary Lautt / Jimmy Caveney / Kalia Klaban</t>
-        </is>
-      </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>AUTOACCEPTED / MATCHED / MATCHED</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>2a8ad0dbe8</t>
-        </is>
-      </c>
-      <c r="G18" s="15" t="inlineStr">
-        <is>
-          <t>66a5ee0b-abd2-5b24-9d53-5c4f6e3fee14 / df329352-6f3b-5e98-b23b-1af6737d100b / 0c681fd1-e4bf-54b3-a314-41da581ecb40</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>Women's Dbls Net</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>Place</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>Player(s)</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>Canon Name</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E20" s="14" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>Person ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>Rita Buckley / Misty Helme</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>Rita Buckley / Misty Helms</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED / AUTOACCEPTED</t>
-        </is>
-      </c>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="inlineStr">
-        <is>
-          <t>2a8ad0dbe8</t>
-        </is>
-      </c>
-      <c r="G21" s="15" t="inlineStr">
-        <is>
-          <t>2b77bf53-5fb8-57a3-a5c0-aa9b0b08434e / e85a6af9-3ac6-550d-8b35-045ec4886d06</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr"/>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>UNRESOLVED</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>2a8ad0dbe8</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Ken Shults</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Kenneth Shults</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>OLD_RESULTS</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>db24e71377</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>2a6a7c9e-1d8a-4f9a-a8f5-6f3a3c1e9b0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Dave Hill</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Dave Hill</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>OLD_RESULTS</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>db24e71377</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>5cb79fb4-ab20-558f-b4a2-e7206c9f22df</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Team Consecutive Kicks</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>Place</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Player(s)</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>Canon Name</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>Source File</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>Person ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Kalia Klaban / Gary Lautt / Jim Caveney</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Kalia Klaban / Gary Lautt / Jimmy Caveney</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>MATCHED / MATCHED / MATCHED</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>OLD_RESULTS</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>db24e71377</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>0c681fd1-e4bf-54b3-a314-41da581ecb40 / 66a5ee0b-abd2-5b24-9d53-5c4f6e3fee14 / df329352-6f3b-5e98-b23b-1af6737d100b</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>Women's Doubles Net</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>Place</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Player(s)</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>Canon Name</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>Source File</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>Person ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Rita Buckley / Misty Helms</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Rita Buckley / Misty Helms</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>MATCHED / MATCHED</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>OLD_RESULTS</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>db24e71377</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>2b77bf53-5fb8-57a3-a5c0-aa9b0b08434e / e85a6af9-3ac6-550d-8b35-045ec4886d06</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr"/>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>NOISE</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>OLD_RESULTS</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>db24e71377</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>Lori Jean Conover / Jennifer Reese</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>Lori Jean Conover / Jennifer Reese</t>
         </is>
       </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="D32" s="15" t="inlineStr">
         <is>
           <t>MATCHED / MATCHED</t>
         </is>
       </c>
-      <c r="E23" s="15" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F23" s="15" t="inlineStr">
-        <is>
-          <t>2a8ad0dbe8</t>
-        </is>
-      </c>
-      <c r="G23" s="15" t="inlineStr">
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>OLD_RESULTS</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>db24e71377</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
         <is>
           <t>77f0f32d-98bf-5742-8228-4e06ac07bd9d / 8d03383e-8e17-5065-a3ec-bae127aea67d</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>Women's Sgls Consecutive</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>Place</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>Player(s)</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>Canon Name</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E25" s="14" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>Person ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>Kalia Klaban</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="inlineStr">
-        <is>
-          <t>Kalia Klaban</t>
-        </is>
-      </c>
-      <c r="D26" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="E26" s="15" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F26" s="15" t="inlineStr">
-        <is>
-          <t>2a8ad0dbe8</t>
-        </is>
-      </c>
-      <c r="G26" s="15" t="inlineStr">
-        <is>
-          <t>0c681fd1-e4bf-54b3-a314-41da581ecb40</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>Women's Sgls Net</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>Place</t>
-        </is>
-      </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>Player(s)</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="inlineStr">
-        <is>
-          <t>Canon Name</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="G28" s="14" t="inlineStr">
-        <is>
-          <t>Person ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="16" t="inlineStr"/>
-      <c r="B29" s="16" t="inlineStr"/>
-      <c r="C29" s="16" t="inlineStr"/>
-      <c r="D29" s="16" t="inlineStr"/>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>2a8ad0dbe8</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>1981 NHSA</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>Sources: OLD_RESULTS  |  ID: b9540daaab  |  SINGLE_SOURCE</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>Doubles Net</t>
+          <t>Women's Singles Consecutive Kicks</t>
         </is>
       </c>
     </row>
@@ -31984,17 +31250,17 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>Mag Hughes / Bill Hayne</t>
+          <t>Kalia Klaban</t>
         </is>
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>Mag Hughes / Bill Hayne</t>
+          <t>Kalia Klaban</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>MATCHED / MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="E35" s="15" t="inlineStr">
@@ -32009,997 +31275,154 @@
       </c>
       <c r="G35" s="15" t="inlineStr">
         <is>
-          <t>ca63a7da-a00a-5a83-ae43-2e17b5758fc8 / 92b0ee3b-efaa-545a-b07e-30ab6d8ebeb0</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="n">
+          <t>0c681fd1-e4bf-54b3-a314-41da581ecb40</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>1981 World Footbag Championships</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Location: Portland, Oregon  |  Sources: FBW  |  ID: 1981_worlds_portland  |  SINGLE_SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>Open Singles</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>Place</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>Player(s)</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>Canon Name</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>Source File</t>
+        </is>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>Person ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>John Stalberger</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>John Stalberger</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="inlineStr">
+        <is>
+          <t>278d51be6e</t>
+        </is>
+      </c>
+      <c r="G41" s="15" t="inlineStr">
+        <is>
+          <t>8f420eba-d663-5f06-b0f4-b62bf7550f80</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t>John Stalberger / Max Smith</t>
-        </is>
-      </c>
-      <c r="C36" s="15" t="inlineStr">
-        <is>
-          <t>John Stalberger / Max Smith</t>
-        </is>
-      </c>
-      <c r="D36" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED / MATCHED</t>
-        </is>
-      </c>
-      <c r="E36" s="15" t="inlineStr">
-        <is>
-          <t>OLD_RESULTS</t>
-        </is>
-      </c>
-      <c r="F36" s="15" t="inlineStr">
-        <is>
-          <t>db24e71377</t>
-        </is>
-      </c>
-      <c r="G36" s="15" t="inlineStr">
-        <is>
-          <t>8f420eba-d663-5f06-b0f4-b62bf7550f80 / 95fb4def-7ff2-5c9c-8de5-1b97d0e13756</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B37" s="15" t="inlineStr">
-        <is>
-          <t>Ken Shults / Walt Mason</t>
-        </is>
-      </c>
-      <c r="C37" s="15" t="inlineStr">
-        <is>
-          <t>Kenneth Shults / Walt Mason</t>
-        </is>
-      </c>
-      <c r="D37" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED / MATCHED</t>
-        </is>
-      </c>
-      <c r="E37" s="15" t="inlineStr">
-        <is>
-          <t>OLD_RESULTS</t>
-        </is>
-      </c>
-      <c r="F37" s="15" t="inlineStr">
-        <is>
-          <t>db24e71377</t>
-        </is>
-      </c>
-      <c r="G37" s="15" t="inlineStr">
-        <is>
-          <t>2a6a7c9e-1d8a-4f9a-a8f5-6f3a3c1e9b0f / c0592850-ae68-5b8b-aaf2-2741b8bdc51d</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="13" t="inlineStr">
-        <is>
-          <t>Intermediate Doubles Net</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="14" t="inlineStr">
-        <is>
-          <t>Place</t>
-        </is>
-      </c>
-      <c r="B39" s="14" t="inlineStr">
-        <is>
-          <t>Player(s)</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="inlineStr">
-        <is>
-          <t>Canon Name</t>
-        </is>
-      </c>
-      <c r="D39" s="14" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E39" s="14" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>Person ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B40" s="15" t="inlineStr">
-        <is>
-          <t>Mike Harding / Mark Daniels</t>
-        </is>
-      </c>
-      <c r="C40" s="15" t="inlineStr">
-        <is>
-          <t>Mike Harding / Mark Daniels</t>
-        </is>
-      </c>
-      <c r="D40" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED / MATCHED</t>
-        </is>
-      </c>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
-          <t>OLD_RESULTS</t>
-        </is>
-      </c>
-      <c r="F40" s="15" t="inlineStr">
-        <is>
-          <t>db24e71377</t>
-        </is>
-      </c>
-      <c r="G40" s="15" t="inlineStr">
-        <is>
-          <t>d75b5871-83c1-5284-b09d-a5eb5d4377dd / 33e83366-7b1e-5c4a-99a9-8eba0d3988ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="13" t="inlineStr">
-        <is>
-          <t>Intermediate Singles Consecutive Kicks</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="14" t="inlineStr">
-        <is>
-          <t>Place</t>
-        </is>
-      </c>
-      <c r="B42" s="14" t="inlineStr">
-        <is>
-          <t>Player(s)</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="inlineStr">
-        <is>
-          <t>Canon Name</t>
-        </is>
-      </c>
-      <c r="D42" s="14" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E42" s="14" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="F42" s="14" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>Person ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>Max Smith</t>
-        </is>
-      </c>
-      <c r="C43" s="15" t="inlineStr">
-        <is>
-          <t>Max Smith</t>
-        </is>
-      </c>
-      <c r="D43" s="15" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>Mike Marshall</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>Mike Marshall</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>MATCHED</t>
         </is>
       </c>
-      <c r="E43" s="15" t="inlineStr">
-        <is>
-          <t>OLD_RESULTS</t>
-        </is>
-      </c>
-      <c r="F43" s="15" t="inlineStr">
-        <is>
-          <t>db24e71377</t>
-        </is>
-      </c>
-      <c r="G43" s="15" t="inlineStr">
-        <is>
-          <t>95fb4def-7ff2-5c9c-8de5-1b97d0e13756</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="13" t="inlineStr">
-        <is>
-          <t>Intermediate Singles Net</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="14" t="inlineStr">
-        <is>
-          <t>Place</t>
-        </is>
-      </c>
-      <c r="B45" s="14" t="inlineStr">
-        <is>
-          <t>Player(s)</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="inlineStr">
-        <is>
-          <t>Canon Name</t>
-        </is>
-      </c>
-      <c r="D45" s="14" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E45" s="14" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="F45" s="14" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>Person ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B46" s="15" t="inlineStr">
-        <is>
-          <t>Mike Harding</t>
-        </is>
-      </c>
-      <c r="C46" s="15" t="inlineStr">
-        <is>
-          <t>Mike Harding</t>
-        </is>
-      </c>
-      <c r="D46" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="E46" s="15" t="inlineStr">
-        <is>
-          <t>OLD_RESULTS</t>
-        </is>
-      </c>
-      <c r="F46" s="15" t="inlineStr">
-        <is>
-          <t>db24e71377</t>
-        </is>
-      </c>
-      <c r="G46" s="15" t="inlineStr">
-        <is>
-          <t>d75b5871-83c1-5284-b09d-a5eb5d4377dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="13" t="inlineStr">
-        <is>
-          <t>Singles Consecutive Kicks</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="14" t="inlineStr">
-        <is>
-          <t>Place</t>
-        </is>
-      </c>
-      <c r="B48" s="14" t="inlineStr">
-        <is>
-          <t>Player(s)</t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="inlineStr">
-        <is>
-          <t>Canon Name</t>
-        </is>
-      </c>
-      <c r="D48" s="14" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E48" s="14" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="F48" s="14" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>Person ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>Gary Lautt</t>
-        </is>
-      </c>
-      <c r="C49" s="15" t="inlineStr">
-        <is>
-          <t>Gary Lautt</t>
-        </is>
-      </c>
-      <c r="D49" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="E49" s="15" t="inlineStr">
-        <is>
-          <t>OLD_RESULTS</t>
-        </is>
-      </c>
-      <c r="F49" s="15" t="inlineStr">
-        <is>
-          <t>db24e71377</t>
-        </is>
-      </c>
-      <c r="G49" s="15" t="inlineStr">
-        <is>
-          <t>66a5ee0b-abd2-5b24-9d53-5c4f6e3fee14</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>Singles Net</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="14" t="inlineStr">
-        <is>
-          <t>Place</t>
-        </is>
-      </c>
-      <c r="B51" s="14" t="inlineStr">
-        <is>
-          <t>Player(s)</t>
-        </is>
-      </c>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>Canon Name</t>
-        </is>
-      </c>
-      <c r="D51" s="14" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E51" s="14" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="F51" s="14" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>Person ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B52" s="15" t="inlineStr">
-        <is>
-          <t>John Stalberger</t>
-        </is>
-      </c>
-      <c r="C52" s="15" t="inlineStr">
-        <is>
-          <t>John Stalberger</t>
-        </is>
-      </c>
-      <c r="D52" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="E52" s="15" t="inlineStr">
-        <is>
-          <t>OLD_RESULTS</t>
-        </is>
-      </c>
-      <c r="F52" s="15" t="inlineStr">
-        <is>
-          <t>db24e71377</t>
-        </is>
-      </c>
-      <c r="G52" s="15" t="inlineStr">
-        <is>
-          <t>8f420eba-d663-5f06-b0f4-b62bf7550f80</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B53" s="15" t="inlineStr">
-        <is>
-          <t>Ken Shults</t>
-        </is>
-      </c>
-      <c r="C53" s="15" t="inlineStr">
-        <is>
-          <t>Kenneth Shults</t>
-        </is>
-      </c>
-      <c r="D53" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="E53" s="15" t="inlineStr">
-        <is>
-          <t>OLD_RESULTS</t>
-        </is>
-      </c>
-      <c r="F53" s="15" t="inlineStr">
-        <is>
-          <t>db24e71377</t>
-        </is>
-      </c>
-      <c r="G53" s="15" t="inlineStr">
-        <is>
-          <t>2a6a7c9e-1d8a-4f9a-a8f5-6f3a3c1e9b0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B54" s="15" t="inlineStr">
-        <is>
-          <t>Dave Hill</t>
-        </is>
-      </c>
-      <c r="C54" s="15" t="inlineStr">
-        <is>
-          <t>Dave Hill</t>
-        </is>
-      </c>
-      <c r="D54" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="E54" s="15" t="inlineStr">
-        <is>
-          <t>OLD_RESULTS</t>
-        </is>
-      </c>
-      <c r="F54" s="15" t="inlineStr">
-        <is>
-          <t>db24e71377</t>
-        </is>
-      </c>
-      <c r="G54" s="15" t="inlineStr">
-        <is>
-          <t>5cb79fb4-ab20-558f-b4a2-e7206c9f22df</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="13" t="inlineStr">
-        <is>
-          <t>Team Consecutive Kicks</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="14" t="inlineStr">
-        <is>
-          <t>Place</t>
-        </is>
-      </c>
-      <c r="B56" s="14" t="inlineStr">
-        <is>
-          <t>Player(s)</t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="inlineStr">
-        <is>
-          <t>Canon Name</t>
-        </is>
-      </c>
-      <c r="D56" s="14" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E56" s="14" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="F56" s="14" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="G56" s="14" t="inlineStr">
-        <is>
-          <t>Person ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B57" s="15" t="inlineStr">
-        <is>
-          <t>Kalia Klaban / Gary Lautt / Jim Caveney</t>
-        </is>
-      </c>
-      <c r="C57" s="15" t="inlineStr">
-        <is>
-          <t>Kalia Klaban / Gary Lautt / Jimmy Caveney</t>
-        </is>
-      </c>
-      <c r="D57" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED / MATCHED / MATCHED</t>
-        </is>
-      </c>
-      <c r="E57" s="15" t="inlineStr">
-        <is>
-          <t>OLD_RESULTS</t>
-        </is>
-      </c>
-      <c r="F57" s="15" t="inlineStr">
-        <is>
-          <t>db24e71377</t>
-        </is>
-      </c>
-      <c r="G57" s="15" t="inlineStr">
-        <is>
-          <t>0c681fd1-e4bf-54b3-a314-41da581ecb40 / 66a5ee0b-abd2-5b24-9d53-5c4f6e3fee14 / df329352-6f3b-5e98-b23b-1af6737d100b</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="13" t="inlineStr">
-        <is>
-          <t>Women's Doubles Net</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="14" t="inlineStr">
-        <is>
-          <t>Place</t>
-        </is>
-      </c>
-      <c r="B59" s="14" t="inlineStr">
-        <is>
-          <t>Player(s)</t>
-        </is>
-      </c>
-      <c r="C59" s="14" t="inlineStr">
-        <is>
-          <t>Canon Name</t>
-        </is>
-      </c>
-      <c r="D59" s="14" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E59" s="14" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="F59" s="14" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="G59" s="14" t="inlineStr">
-        <is>
-          <t>Person ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t>Rita Buckley / Misty Helms</t>
-        </is>
-      </c>
-      <c r="C60" s="15" t="inlineStr">
-        <is>
-          <t>Rita Buckley / Misty Helms</t>
-        </is>
-      </c>
-      <c r="D60" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED / MATCHED</t>
-        </is>
-      </c>
-      <c r="E60" s="15" t="inlineStr">
-        <is>
-          <t>OLD_RESULTS</t>
-        </is>
-      </c>
-      <c r="F60" s="15" t="inlineStr">
-        <is>
-          <t>db24e71377</t>
-        </is>
-      </c>
-      <c r="G60" s="15" t="inlineStr">
-        <is>
-          <t>2b77bf53-5fb8-57a3-a5c0-aa9b0b08434e / e85a6af9-3ac6-550d-8b35-045ec4886d06</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="B61" s="18" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="inlineStr"/>
-      <c r="D61" s="18" t="inlineStr">
-        <is>
-          <t>NOISE</t>
-        </is>
-      </c>
-      <c r="E61" s="18" t="inlineStr">
-        <is>
-          <t>OLD_RESULTS</t>
-        </is>
-      </c>
-      <c r="F61" s="18" t="inlineStr">
-        <is>
-          <t>db24e71377</t>
-        </is>
-      </c>
-      <c r="G61" s="18" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B62" s="15" t="inlineStr">
-        <is>
-          <t>Lori Jean Conover / Jennifer Reese</t>
-        </is>
-      </c>
-      <c r="C62" s="15" t="inlineStr">
-        <is>
-          <t>Lori Jean Conover / Jennifer Reese</t>
-        </is>
-      </c>
-      <c r="D62" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED / MATCHED</t>
-        </is>
-      </c>
-      <c r="E62" s="15" t="inlineStr">
-        <is>
-          <t>OLD_RESULTS</t>
-        </is>
-      </c>
-      <c r="F62" s="15" t="inlineStr">
-        <is>
-          <t>db24e71377</t>
-        </is>
-      </c>
-      <c r="G62" s="15" t="inlineStr">
-        <is>
-          <t>77f0f32d-98bf-5742-8228-4e06ac07bd9d / 8d03383e-8e17-5065-a3ec-bae127aea67d</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="13" t="inlineStr">
-        <is>
-          <t>Women's Singles Consecutive Kicks</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="14" t="inlineStr">
-        <is>
-          <t>Place</t>
-        </is>
-      </c>
-      <c r="B64" s="14" t="inlineStr">
-        <is>
-          <t>Player(s)</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="inlineStr">
-        <is>
-          <t>Canon Name</t>
-        </is>
-      </c>
-      <c r="D64" s="14" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E64" s="14" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="F64" s="14" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="G64" s="14" t="inlineStr">
-        <is>
-          <t>Person ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B65" s="15" t="inlineStr">
-        <is>
-          <t>Kalia Klaban</t>
-        </is>
-      </c>
-      <c r="C65" s="15" t="inlineStr">
-        <is>
-          <t>Kalia Klaban</t>
-        </is>
-      </c>
-      <c r="D65" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="E65" s="15" t="inlineStr">
-        <is>
-          <t>OLD_RESULTS</t>
-        </is>
-      </c>
-      <c r="F65" s="15" t="inlineStr">
-        <is>
-          <t>db24e71377</t>
-        </is>
-      </c>
-      <c r="G65" s="15" t="inlineStr">
-        <is>
-          <t>0c681fd1-e4bf-54b3-a314-41da581ecb40</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="11" t="inlineStr">
-        <is>
-          <t>1981 World Footbag Championships</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="12" t="inlineStr">
-        <is>
-          <t>Location: Portland, Oregon  |  Sources: FBW  |  ID: af9e865ed5  |  SINGLE_SOURCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="13" t="inlineStr">
-        <is>
-          <t>Open Singles</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="14" t="inlineStr">
-        <is>
-          <t>Place</t>
-        </is>
-      </c>
-      <c r="B70" s="14" t="inlineStr">
-        <is>
-          <t>Player(s)</t>
-        </is>
-      </c>
-      <c r="C70" s="14" t="inlineStr">
-        <is>
-          <t>Canon Name</t>
-        </is>
-      </c>
-      <c r="D70" s="14" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E70" s="14" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="F70" s="14" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-      <c r="G70" s="14" t="inlineStr">
-        <is>
-          <t>Person ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B71" s="15" t="inlineStr">
-        <is>
-          <t>John Stalberger</t>
-        </is>
-      </c>
-      <c r="C71" s="15" t="inlineStr">
-        <is>
-          <t>John Stalberger</t>
-        </is>
-      </c>
-      <c r="D71" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="E71" s="15" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F71" s="15" t="inlineStr">
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
         <is>
           <t>278d51be6e</t>
         </is>
       </c>
-      <c r="G71" s="15" t="inlineStr">
-        <is>
-          <t>8f420eba-d663-5f06-b0f4-b62bf7550f80</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B72" s="15" t="inlineStr">
-        <is>
-          <t>Mike Marshall</t>
-        </is>
-      </c>
-      <c r="C72" s="15" t="inlineStr">
-        <is>
-          <t>Mike Marshall</t>
-        </is>
-      </c>
-      <c r="D72" s="15" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="E72" s="15" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F72" s="15" t="inlineStr">
-        <is>
-          <t>278d51be6e</t>
-        </is>
-      </c>
-      <c r="G72" s="15" t="inlineStr">
+      <c r="G42" s="15" t="inlineStr">
         <is>
           <t>1381939c-35d0-5941-ae91-ca262b6fc482</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="A32:G32"/>
+  <mergeCells count="14">
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A38:G38"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A63:G63"/>
-    <mergeCell ref="A68:G68"/>
-    <mergeCell ref="A44:G44"/>
-    <mergeCell ref="A58:G58"/>
-    <mergeCell ref="A67:G67"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A33:G33"/>
     <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A69:G69"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A55:G55"/>
-    <mergeCell ref="A50:G50"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33033,7 +31456,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Sources: FBW|OLD_RESULTS  |  ID: 1e36e7ca92  |  CONFIRMED_MULTI_SOURCE</t>
+          <t>Sources: FBW|OLD_RESULTS  |  ID: 1982_worlds  |  CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
     </row>
@@ -33683,12 +32106,12 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Steve Femmel / Ted Johnson</t>
+          <t>Steve Fennell / Ted Johnson</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>Steve Femmel / Ted Johnson</t>
+          <t>Steve Fennell / Ted Johnson</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
@@ -33841,12 +32264,12 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Steve Femmel</t>
+          <t>Steve Fennell</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>Steve Femmel</t>
+          <t>Steve Fennell</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
@@ -35335,35 +33758,35 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="17" t="n">
+      <c r="A82" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B82" s="17" t="inlineStr">
+      <c r="B82" s="16" t="inlineStr">
         <is>
           <t>Karen Uppinghouse / Cheryl Hughes</t>
         </is>
       </c>
-      <c r="C82" s="17" t="inlineStr">
+      <c r="C82" s="16" t="inlineStr">
         <is>
           <t>Karen Uppinghouse / Cheryl Hughes</t>
         </is>
       </c>
-      <c r="D82" s="17" t="inlineStr">
+      <c r="D82" s="16" t="inlineStr">
         <is>
           <t>NEW_PLAYER / MATCHED</t>
         </is>
       </c>
-      <c r="E82" s="17" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F82" s="17" t="inlineStr">
+      <c r="E82" s="16" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="F82" s="16" t="inlineStr">
         <is>
           <t>38240bb7ec</t>
         </is>
       </c>
-      <c r="G82" s="17" t="inlineStr">
+      <c r="G82" s="16" t="inlineStr">
         <is>
           <t>4b3d47c0-977c-5285-a31f-b3c2f33428a8 / cfcef53f-670c-5721-b206-1ebe7d63987c</t>
         </is>
@@ -35826,7 +34249,7 @@
     <row r="100">
       <c r="A100" s="12" t="inlineStr">
         <is>
-          <t>Location: Seattle, WA  |  Sources: FBW  |  ID: e41e20722d  |  SINGLE_SOURCE</t>
+          <t>Location: Seattle, WA  |  Sources: FBW  |  ID: 1982_western_regionals  |  SINGLE_SOURCE</t>
         </is>
       </c>
     </row>
@@ -35919,7 +34342,7 @@
     <row r="106">
       <c r="A106" s="12" t="inlineStr">
         <is>
-          <t>Location: Portland, Oregon  |  Sources: FBW  |  ID: f771c4ef26  |  SINGLE_SOURCE</t>
+          <t>Location: Portland, Oregon  |  Sources: FBW  |  ID: 1982_worlds_portland  |  SINGLE_SOURCE</t>
         </is>
       </c>
     </row>
@@ -36066,7 +34489,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Sources: FBW|OLD_RESULTS  |  ID: 76498d51d2  |  CONFIRMED_MULTI_SOURCE</t>
+          <t>Sources: FBW|OLD_RESULTS  |  ID: 1983_worlds_nhsa  |  CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
     </row>
@@ -36264,35 +34687,35 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="n">
+      <c r="A10" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Steve Brown / Kevin Gaunce</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>Steve Brown / Kevin Gaunce</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>NEW_PLAYER / NEW_PLAYER</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>OLD_RESULTS</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>30f5a76d81</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>7d9fad30-f7f8-569b-b27d-7ef146e35653 / bf2fefd4-7e20-5b87-84ba-056eac2bb001</t>
         </is>
@@ -38850,7 +37273,7 @@
     <row r="99">
       <c r="A99" s="12" t="inlineStr">
         <is>
-          <t>Location: Oregon  |  Sources: FBW  |  ID: 0a43031545  |  SINGLE_SOURCE</t>
+          <t>Location: Oregon  |  Sources: FBW  |  ID: 1983_oregon_state  |  SINGLE_SOURCE</t>
         </is>
       </c>
     </row>
@@ -38943,7 +37366,7 @@
     <row r="105">
       <c r="A105" s="12" t="inlineStr">
         <is>
-          <t>Sources: FBW|OLD_RESULTS  |  ID: 00659874b9  |  CONFIRMED_MULTI_SOURCE</t>
+          <t>Sources: FBW|OLD_RESULTS  |  ID: 1983_worlds_wfa  |  CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
     </row>
@@ -39772,58 +38195,58 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="16" t="n">
+      <c r="A134" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B134" s="16" t="inlineStr">
+      <c r="B134" s="18" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C134" s="16" t="inlineStr"/>
-      <c r="D134" s="16" t="inlineStr">
+      <c r="C134" s="18" t="inlineStr"/>
+      <c r="D134" s="18" t="inlineStr">
         <is>
           <t>UNRESOLVED</t>
         </is>
       </c>
-      <c r="E134" s="16" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F134" s="16" t="inlineStr">
+      <c r="E134" s="18" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="F134" s="18" t="inlineStr">
         <is>
           <t>d7766289c6</t>
         </is>
       </c>
-      <c r="G134" s="16" t="inlineStr"/>
+      <c r="G134" s="18" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="16" t="n">
+      <c r="A135" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B135" s="16" t="inlineStr">
+      <c r="B135" s="18" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C135" s="16" t="inlineStr"/>
-      <c r="D135" s="16" t="inlineStr">
+      <c r="C135" s="18" t="inlineStr"/>
+      <c r="D135" s="18" t="inlineStr">
         <is>
           <t>UNRESOLVED</t>
         </is>
       </c>
-      <c r="E135" s="16" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F135" s="16" t="inlineStr">
+      <c r="E135" s="18" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="F135" s="18" t="inlineStr">
         <is>
           <t>d7766289c6</t>
         </is>
       </c>
-      <c r="G135" s="16" t="inlineStr"/>
+      <c r="G135" s="18" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
@@ -40108,7 +38531,7 @@
       </c>
       <c r="C146" s="15" t="inlineStr">
         <is>
-          <t>Steve Femmel</t>
+          <t>Steve Fennell</t>
         </is>
       </c>
       <c r="D146" s="15" t="inlineStr">
@@ -40743,12 +39166,12 @@
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>Steve Femmel</t>
+          <t>Steve Fennell</t>
         </is>
       </c>
       <c r="C168" s="15" t="inlineStr">
         <is>
-          <t>Steve Femmel</t>
+          <t>Steve Fennell</t>
         </is>
       </c>
       <c r="D168" s="15" t="inlineStr">
@@ -41185,35 +39608,35 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="17" t="n">
+      <c r="A183" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B183" s="17" t="inlineStr">
+      <c r="B183" s="16" t="inlineStr">
         <is>
           <t>Karin Atogpian / Constance Constable</t>
         </is>
       </c>
-      <c r="C183" s="17" t="inlineStr">
+      <c r="C183" s="16" t="inlineStr">
         <is>
           <t>Karen Atgopian / Constance Constable</t>
         </is>
       </c>
-      <c r="D183" s="17" t="inlineStr">
+      <c r="D183" s="16" t="inlineStr">
         <is>
           <t>NEW_PLAYER / MATCHED</t>
         </is>
       </c>
-      <c r="E183" s="17" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F183" s="17" t="inlineStr">
+      <c r="E183" s="16" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="F183" s="16" t="inlineStr">
         <is>
           <t>d7766289c6</t>
         </is>
       </c>
-      <c r="G183" s="17" t="inlineStr">
+      <c r="G183" s="16" t="inlineStr">
         <is>
           <t>86de3135-51c7-5ad5-9144-112f984acd3f / 826201f8-2540-5663-9bbf-239e94ccee43</t>
         </is>
@@ -41334,35 +39757,35 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="17" t="n">
+      <c r="A188" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B188" s="17" t="inlineStr">
+      <c r="B188" s="16" t="inlineStr">
         <is>
           <t>Karen Atgopian / Constance Constable</t>
         </is>
       </c>
-      <c r="C188" s="17" t="inlineStr">
+      <c r="C188" s="16" t="inlineStr">
         <is>
           <t>Karen Atgopian / Constance Constable</t>
         </is>
       </c>
-      <c r="D188" s="17" t="inlineStr">
+      <c r="D188" s="16" t="inlineStr">
         <is>
           <t>NEW_PLAYER / MATCHED</t>
         </is>
       </c>
-      <c r="E188" s="17" t="inlineStr">
+      <c r="E188" s="16" t="inlineStr">
         <is>
           <t>OLD_RESULTS</t>
         </is>
       </c>
-      <c r="F188" s="17" t="inlineStr">
+      <c r="F188" s="16" t="inlineStr">
         <is>
           <t>9bb67e459b</t>
         </is>
       </c>
-      <c r="G188" s="17" t="inlineStr">
+      <c r="G188" s="16" t="inlineStr">
         <is>
           <t>86de3135-51c7-5ad5-9144-112f984acd3f / 826201f8-2540-5663-9bbf-239e94ccee43</t>
         </is>
@@ -41676,7 +40099,7 @@
     <row r="201">
       <c r="A201" s="12" t="inlineStr">
         <is>
-          <t>Location: Portland, Oregon  |  Sources: FBW  |  ID: 76ff377548  |  SINGLE_SOURCE</t>
+          <t>Location: Portland, Oregon  |  Sources: FBW  |  ID: 1983_worlds_portland  |  SINGLE_SOURCE</t>
         </is>
       </c>
     </row>
@@ -41839,35 +40262,35 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="17" t="n">
+      <c r="A208" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B208" s="17" t="inlineStr">
+      <c r="B208" s="16" t="inlineStr">
         <is>
           <t>Ken Eldrick</t>
         </is>
       </c>
-      <c r="C208" s="17" t="inlineStr">
+      <c r="C208" s="16" t="inlineStr">
         <is>
           <t>Ken Eldrick</t>
         </is>
       </c>
-      <c r="D208" s="17" t="inlineStr">
+      <c r="D208" s="16" t="inlineStr">
         <is>
           <t>NEW_PLAYER</t>
         </is>
       </c>
-      <c r="E208" s="17" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F208" s="17" t="inlineStr">
+      <c r="E208" s="16" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="F208" s="16" t="inlineStr">
         <is>
           <t>9bfd1a7567</t>
         </is>
       </c>
-      <c r="G208" s="17" t="inlineStr">
+      <c r="G208" s="16" t="inlineStr">
         <is>
           <t>03bcdedb-b187-5ef3-ba2d-e371c1cada15</t>
         </is>
@@ -41959,7 +40382,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Sources: FBW|OLD_RESULTS  |  ID: 6cd9e5b635  |  CONFIRMED_MULTI_SOURCE</t>
+          <t>Sources: FBW|OLD_RESULTS  |  ID: 1984_worlds  |  CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
     </row>
@@ -43218,35 +41641,35 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="17" t="n">
+      <c r="A47" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B47" s="17" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>Doug Little</t>
         </is>
       </c>
-      <c r="C47" s="17" t="inlineStr">
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>Doug Little</t>
         </is>
       </c>
-      <c r="D47" s="17" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>NEW_PLAYER</t>
         </is>
       </c>
-      <c r="E47" s="17" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F47" s="17" t="inlineStr">
+      <c r="E47" s="16" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
         <is>
           <t>dab11f565e</t>
         </is>
       </c>
-      <c r="G47" s="17" t="inlineStr">
+      <c r="G47" s="16" t="inlineStr">
         <is>
           <t>d86e1aad-2058-5773-95eb-c5fd05217112</t>
         </is>
@@ -45208,7 +43631,7 @@
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
         <is>
-          <t>Sources: FBW  |  ID: 77aa0f8390  |  SINGLE_SOURCE</t>
+          <t>Sources: FBW  |  ID: 1984_euro_champs  |  SINGLE_SOURCE</t>
         </is>
       </c>
     </row>
@@ -45257,35 +43680,35 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="17" t="n">
+      <c r="A119" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B119" s="17" t="inlineStr">
+      <c r="B119" s="16" t="inlineStr">
         <is>
           <t>Jan-Olof Karlsson</t>
         </is>
       </c>
-      <c r="C119" s="17" t="inlineStr">
+      <c r="C119" s="16" t="inlineStr">
         <is>
           <t>Jan-Olof Karlsson</t>
         </is>
       </c>
-      <c r="D119" s="17" t="inlineStr">
+      <c r="D119" s="16" t="inlineStr">
         <is>
           <t>NEW_PLAYER</t>
         </is>
       </c>
-      <c r="E119" s="17" t="inlineStr">
-        <is>
-          <t>FBW</t>
-        </is>
-      </c>
-      <c r="F119" s="17" t="inlineStr">
+      <c r="E119" s="16" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="F119" s="16" t="inlineStr">
         <is>
           <t>da1be2ed69</t>
         </is>
       </c>
-      <c r="G119" s="17" t="inlineStr">
+      <c r="G119" s="16" t="inlineStr">
         <is>
           <t>6448a460-2f45-5a41-879d-f967d87e8a5c</t>
         </is>
@@ -45301,7 +43724,7 @@
     <row r="122">
       <c r="A122" s="12" t="inlineStr">
         <is>
-          <t>Sources: FBW|OLD_RESULTS  |  ID: 0e1499ab21  |  CONFIRMED_MULTI_SOURCE</t>
+          <t>Sources: FBW|OLD_RESULTS  |  ID: 1984_wfa_nationals  |  CONFIRMED_MULTI_SOURCE</t>
         </is>
       </c>
     </row>

--- a/early_data/out/footbag_results_pre1997_v1.xlsx
+++ b/early_data/out/footbag_results_pre1997_v1.xlsx
@@ -26208,7 +26208,7 @@
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>Women's Dbls Net</t>
+          <t>Mixed Doubles Net</t>
         </is>
       </c>
       <c r="G2" s="8" t="inlineStr">
@@ -26278,7 +26278,7 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>Open Sgls Consecutiv</t>
+          <t>Open Dbls Consecutiv</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Ultra Doubles Net</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Doubles Net</t>
+          <t>Mixed Doubles Net</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -26418,7 +26418,7 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Doubles Net</t>
+          <t>Open Dbls Net</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -26519,7 +26519,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Women's Dbls Net</t>
+          <t>Women's Sgls Net</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -26589,7 +26589,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Women's Dbls Net</t>
+          <t>Mixed Doubles Net</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -26624,7 +26624,7 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>Golf</t>
+          <t>Open Dbls Consecutiv</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
@@ -26694,7 +26694,7 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>Women's Doubles Cons</t>
+          <t>Mixed Doubles Net</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
@@ -26764,7 +26764,7 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>Doubles Net</t>
+          <t>Singles Net</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
@@ -26799,7 +26799,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Open Sgls Net</t>
+          <t>Open Dbls Consecutiv</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -26834,7 +26834,7 @@
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Mixed Doubles Net</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
@@ -26869,7 +26869,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Open Dbls Consecutiv</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -27009,7 +27009,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doubles Net</t>
+          <t>Open Dbls Net</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doubles Net</t>
+          <t>Open Dbls Net</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -27347,7 +27347,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doubles Consecutive </t>
+          <t>Singles</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -27417,7 +27417,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Women's Dbls Net</t>
+          <t>Women's Freestyle</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -27452,7 +27452,7 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Mixed Doubles Net</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
@@ -27487,7 +27487,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Mixed Doubles Net</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -27522,7 +27522,7 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doubles Consecutive </t>
+          <t>Advanced Doubles Net</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
@@ -27592,7 +27592,7 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>Women's Dbls Net</t>
+          <t>Women's Sgls Net</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
@@ -27697,7 +27697,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Doubles Net</t>
+          <t>Open Singles Net</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -27732,7 +27732,7 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Open Dbls Consecutiv</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
@@ -27767,7 +27767,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Women's Doubles Net</t>
+          <t>Mixed Dbls Net</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -27802,7 +27802,7 @@
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>Team Consecutive Kic</t>
+          <t>Women's Singles Cons</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
@@ -27872,7 +27872,7 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>Women's Singles Net</t>
+          <t>Women's Sgls Net</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
@@ -27942,7 +27942,7 @@
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>Open Doubles Net</t>
+          <t>Open Singles</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
@@ -28012,7 +28012,7 @@
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Doubles Net</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
@@ -28152,7 +28152,7 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>Women's Freestyle</t>
+          <t>Women's Team Freesty</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
@@ -28222,7 +28222,7 @@
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>Women's Dbls Net</t>
+          <t>Women's Golf</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
@@ -28257,7 +28257,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Women's Dbls Net</t>
+          <t>Mixed Doubles Net</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -28292,7 +28292,7 @@
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Mixed Doubles Net</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
@@ -28327,7 +28327,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Women's Doubles Cons</t>
+          <t>Women's Singles Cons</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -28432,7 +28432,7 @@
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>Doubles Net</t>
+          <t>Intermediate Singles</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
@@ -28467,7 +28467,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Golf</t>
+          <t>Ultra Doubles Net</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -28502,7 +28502,7 @@
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>Open Doubles</t>
+          <t>Open Singles</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
@@ -28572,7 +28572,7 @@
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>Doubles Net</t>
+          <t>Open Dbls Net</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
@@ -28642,7 +28642,7 @@
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>Women's Doubles Cons</t>
+          <t>Women's Sgls Freesty</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
@@ -28677,7 +28677,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doubles Consecutive </t>
+          <t>Open Sgls Consecutiv</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -28883,7 +28883,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Open Freestyle</t>
+          <t>Open Sgls Consecutiv</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -28918,7 +28918,7 @@
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>Women's Dbls Net</t>
+          <t>Mixed Doubles Net</t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr">
@@ -28953,7 +28953,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Open Team Freestyle</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -28988,7 +28988,7 @@
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>Women's Doubles One-</t>
+          <t>Women's Team Freesty</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
@@ -29023,7 +29023,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Ultra Doubles Net</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -29058,7 +29058,7 @@
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>Women's Dbls Net</t>
+          <t>Mixed Doubles Net</t>
         </is>
       </c>
       <c r="G84" s="8" t="inlineStr">
@@ -29198,7 +29198,7 @@
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>Open Sgls Net</t>
+          <t>Open Singles Net</t>
         </is>
       </c>
       <c r="G88" s="8" t="inlineStr">
@@ -29268,7 +29268,7 @@
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>Women's Team Freesty</t>
+          <t>Women's Dbls Net</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
@@ -29478,7 +29478,7 @@
       </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
-          <t>Open Golf</t>
+          <t>Intermediate Doubles</t>
         </is>
       </c>
       <c r="G96" s="8" t="inlineStr">
@@ -29513,7 +29513,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Open Sgls Freestyle</t>
+          <t>Open Team Freestyle</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -29548,7 +29548,7 @@
       </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
-          <t>Women's Doubles Cons</t>
+          <t>Mixed Doubles Net</t>
         </is>
       </c>
       <c r="G98" s="8" t="inlineStr">
@@ -29583,7 +29583,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Women's Dbls Net</t>
+          <t>Mixed Doubles Net</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -29618,7 +29618,7 @@
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
-          <t>Women's Doubles Cons</t>
+          <t>Women's Freestyle</t>
         </is>
       </c>
       <c r="G100" s="8" t="inlineStr">
@@ -29653,7 +29653,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Doubles Net</t>
+          <t>Singles Net</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -29688,7 +29688,7 @@
       </c>
       <c r="F102" s="8" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Open Team Freestyle</t>
         </is>
       </c>
       <c r="G102" s="8" t="inlineStr">
